--- a/BOEproject/Tutorial/Sparkle/sparkle_fit_result.xlsx
+++ b/BOEproject/Tutorial/Sparkle/sparkle_fit_result.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>F:\PHD\GitFiles\diffractsim\BOEproject\sparkle0511\image1.png</t>
+          <t>F:\PHD\GitFiles\diffractsim\BOEproject\Tutorial\imagefiles\image1.png</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -506,7 +506,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>F:\PHD\GitFiles\diffractsim\BOEproject\sparkle0511\image2.png</t>
+          <t>F:\PHD\GitFiles\diffractsim\BOEproject\Tutorial\imagefiles\image2.png</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -536,7 +536,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>F:\PHD\GitFiles\diffractsim\BOEproject\sparkle0511\image3.png</t>
+          <t>F:\PHD\GitFiles\diffractsim\BOEproject\Tutorial\imagefiles\image3.png</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -566,7 +566,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>F:\PHD\GitFiles\diffractsim\BOEproject\sparkle0511\image4.png</t>
+          <t>F:\PHD\GitFiles\diffractsim\BOEproject\Tutorial\imagefiles\image4.png</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>F:\PHD\GitFiles\diffractsim\BOEproject\sparkle0511\image5.png</t>
+          <t>F:\PHD\GitFiles\diffractsim\BOEproject\Tutorial\imagefiles\image5.png</t>
         </is>
       </c>
       <c r="C6" t="n">
